--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_79_R8.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_79_R8.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.789899999999999</v>
+        <v>6.3133</v>
       </c>
       <c r="E2" t="n">
-        <v>2.868</v>
+        <v>1.366</v>
       </c>
       <c r="F2" t="n">
-        <v>5.9218</v>
+        <v>4.9473</v>
       </c>
       <c r="G2" t="n">
         <v>1.3709</v>
@@ -610,13 +610,13 @@
         <v>3.0154</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9577</v>
+        <v>1.4811</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1236</v>
+        <v>0.6216</v>
       </c>
       <c r="U2" t="n">
-        <v>1.8341</v>
+        <v>0.8595</v>
       </c>
       <c r="V2" t="n">
         <v>0.6778999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3206</v>
+        <v>3.2261</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1093</v>
+        <v>2.2837</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2113</v>
+        <v>0.9424</v>
       </c>
       <c r="G3" t="n">
         <v>1.7089</v>
@@ -688,13 +688,13 @@
         <v>0.232</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5216</v>
+        <v>1.4271</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2072</v>
+        <v>0.3815</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3144</v>
+        <v>1.0455</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8727</v>
+        <v>3.1998</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.0518</v>
+        <v>-0.8592</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9245</v>
+        <v>4.0589</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4518</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4121</v>
+        <v>0.7391</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2355</v>
+        <v>-0.0428</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6475</v>
+        <v>0.782</v>
       </c>
       <c r="V4" t="n">
         <v>2.6805</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5816</v>
+        <v>2.6562</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2562</v>
+        <v>-0.1815</v>
       </c>
       <c r="F5" t="n">
         <v>2.8378</v>
@@ -844,10 +844,10 @@
         <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6212</v>
+        <v>0.6959</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.094</v>
+        <v>-0.0193</v>
       </c>
       <c r="U5" t="n">
         <v>0.7151999999999999</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3985</v>
+        <v>0.8777</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.5202</v>
+        <v>-1.9737</v>
       </c>
       <c r="F6" t="n">
-        <v>2.9187</v>
+        <v>2.8515</v>
       </c>
       <c r="G6" t="n">
         <v>-2.6181</v>
@@ -922,13 +922,13 @@
         <v>1.6237</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5526</v>
+        <v>1.0319</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5816</v>
+        <v>-0.0351</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1343</v>
+        <v>1.0671</v>
       </c>
       <c r="V6" t="n">
         <v>1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4309</v>
+        <v>0.6369</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.2259</v>
+        <v>-1.5615</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7951</v>
+        <v>2.1984</v>
       </c>
       <c r="G7" t="n">
         <v>2.6065</v>
@@ -1000,13 +1000,13 @@
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9498</v>
+        <v>0.118</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8136</v>
+        <v>-0.1491</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1362</v>
+        <v>0.2671</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2722</v>
+        <v>-1.0459</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.2755</v>
+        <v>-1.0829</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0033</v>
+        <v>0.0369</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9959</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7402</v>
+        <v>-0.514</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2908</v>
+        <v>-0.0982</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4494</v>
+        <v>-0.4158</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3415</v>
+        <v>-1.9872</v>
       </c>
       <c r="E9" t="n">
-        <v>-8.0662</v>
+        <v>-7.0479</v>
       </c>
       <c r="F9" t="n">
-        <v>4.7247</v>
+        <v>5.0607</v>
       </c>
       <c r="G9" t="n">
         <v>-3.357</v>
@@ -1156,13 +1156,13 @@
         <v>2.7834</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3066</v>
+        <v>1.0477</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0886</v>
+        <v>-0.0703</v>
       </c>
       <c r="U9" t="n">
-        <v>0.782</v>
+        <v>1.118</v>
       </c>
       <c r="V9" t="n">
         <v>-0.1418</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5196</v>
+        <v>-4.1247</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.6346</v>
+        <v>-3.206</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8851</v>
+        <v>-0.9187</v>
       </c>
       <c r="G10" t="n">
         <v>0.5957</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0444</v>
+        <v>0.4393</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3655</v>
+        <v>0.063</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4099</v>
+        <v>0.3763</v>
       </c>
       <c r="V10" t="n">
         <v>-2.1444</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.5591</v>
+        <v>-5.1655</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.8463</v>
+        <v>-6.8896</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2872</v>
+        <v>1.7241</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4828</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0988</v>
+        <v>0.4925</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2794</v>
+        <v>0.2361</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1805</v>
+        <v>0.2563</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.839999999999997</v>
+        <v>4.586700000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>-19.8994</v>
+        <v>-19.1526</v>
       </c>
       <c r="F12" t="n">
         <v>23.7393</v>
@@ -1390,13 +1390,13 @@
         <v>16.2369</v>
       </c>
       <c r="S12" t="n">
-        <v>6.211800000000001</v>
+        <v>6.9586</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1406000000000001</v>
+        <v>0.8874</v>
       </c>
       <c r="U12" t="n">
-        <v>6.071300000000001</v>
+        <v>6.071200000000001</v>
       </c>
       <c r="V12" t="n">
         <v>1.4665</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.1006</v>
+        <v>5.8077</v>
       </c>
       <c r="E13" t="n">
         <v>1.2691</v>
       </c>
       <c r="F13" t="n">
-        <v>3.8316</v>
+        <v>4.5386</v>
       </c>
       <c r="G13" t="n">
         <v>3.2451</v>
@@ -1468,13 +1468,13 @@
         <v>2.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8377</v>
+        <v>-0.1307</v>
       </c>
       <c r="T13" t="n">
         <v>-0.9313</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0936</v>
+        <v>0.8006</v>
       </c>
       <c r="V13" t="n">
         <v>0.1418</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4324</v>
+        <v>3.7355</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4288</v>
+        <v>-0.6647</v>
       </c>
       <c r="F14" t="n">
-        <v>3.8611</v>
+        <v>4.4002</v>
       </c>
       <c r="G14" t="n">
         <v>2.4596</v>
@@ -1546,13 +1546,13 @@
         <v>2.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7257</v>
+        <v>-0.4226</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1766</v>
+        <v>-0.4125</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5491</v>
+        <v>-0.0101</v>
       </c>
       <c r="V14" t="n">
         <v>1.4665</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,58 +1579,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8568</v>
+        <v>0.7771</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.9274</v>
+        <v>-3.0395</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7842</v>
+        <v>3.8166</v>
       </c>
       <c r="G15" t="n">
-        <v>0.8605</v>
+        <v>1.1305</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9975000000000001</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.137</v>
+        <v>0.4919</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4599</v>
+        <v>-0.9207</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2759</v>
+        <v>0.5783</v>
       </c>
       <c r="L15" t="n">
-        <v>0.184</v>
+        <v>-1.4991</v>
       </c>
       <c r="M15" t="n">
-        <v>0.4006</v>
+        <v>2.0512</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7217</v>
+        <v>0.0602</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3211</v>
+        <v>1.991</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R15" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4602</v>
+        <v>-0.2812</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1641</v>
+        <v>-0.727</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2961</v>
+        <v>0.4459</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2711</v>
+        <v>0.059</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.2754</v>
+        <v>-2.107</v>
       </c>
       <c r="F16" t="n">
-        <v>3.5465</v>
+        <v>2.166</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1305</v>
+        <v>0.8605</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4919</v>
+        <v>-0.137</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9207</v>
+        <v>0.4599</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5783</v>
+        <v>0.2759</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.4991</v>
+        <v>0.184</v>
       </c>
       <c r="M16" t="n">
-        <v>2.0512</v>
+        <v>0.4006</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0602</v>
+        <v>0.7217</v>
       </c>
       <c r="O16" t="n">
-        <v>1.991</v>
+        <v>-0.3211</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.3917</v>
+        <v>-2.5515</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7872</v>
+        <v>0.6625</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.963</v>
+        <v>-0.0154</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1757</v>
+        <v>0.6778</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5361</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3637</v>
+        <v>-0.0548</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0604</v>
+        <v>-0.9424</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6967</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="G17" t="n">
         <v>0.4671</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1349</v>
+        <v>0.174</v>
       </c>
       <c r="T17" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.2005</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2175</v>
+        <v>-0.0266</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>J. MOTLEY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7141</v>
+        <v>-0.3996</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.7767</v>
+        <v>-1.9336</v>
       </c>
       <c r="F18" t="n">
-        <v>3.0626</v>
+        <v>1.5341</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1885</v>
+        <v>0.7116</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.605</v>
+        <v>-0.0948</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7935</v>
+        <v>0.8064</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1779</v>
+        <v>-0.0707</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6785</v>
+        <v>0.6421</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8564000000000001</v>
+        <v>-0.7127</v>
       </c>
       <c r="M18" t="n">
-        <v>0.0106</v>
+        <v>0.7823</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9265</v>
+        <v>-0.7369</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9371</v>
+        <v>1.5192</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7834</v>
+        <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2943</v>
+        <v>-1.1086</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.6351</v>
+        <v>-0.845</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3408</v>
+        <v>-0.2636</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>-0.9304</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
         <v>-1.0722</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. ENNIS</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.762</v>
+        <v>-0.7343</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0579</v>
+        <v>-3.3049</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7040999999999999</v>
+        <v>2.5705</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6873</v>
+        <v>0.1885</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3193</v>
+        <v>-1.605</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.368</v>
+        <v>1.7935</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0168</v>
+        <v>0.1779</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0168</v>
+        <v>-0.6785</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7040999999999999</v>
+        <v>0.0106</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3361</v>
+        <v>-0.9265</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.368</v>
+        <v>0.9371</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.7834</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0747</v>
+        <v>-0.3145</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0747</v>
+        <v>-1.1633</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.8487</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. MOTLEY</t>
+          <t>T. ENNIS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1009</v>
+        <v>-0.762</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.0516</v>
+        <v>-0.0579</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9507</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7116</v>
+        <v>-0.6873</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0948</v>
+        <v>-0.3193</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8064</v>
+        <v>-0.368</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0707</v>
+        <v>0.0168</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6421</v>
+        <v>0.0168</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7127</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7823</v>
+        <v>-0.7040999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7369</v>
+        <v>-0.3361</v>
       </c>
       <c r="O20" t="n">
-        <v>1.5192</v>
+        <v>-0.368</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0876</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8099</v>
+        <v>-0.0747</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.963</v>
+        <v>-0.0747</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.847</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9304</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.732</v>
+        <v>-1.8328</v>
       </c>
       <c r="E21" t="n">
         <v>-1.9125</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1805</v>
+        <v>0.07969999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7395</v>
@@ -2092,13 +2092,13 @@
         <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2245</v>
+        <v>-0.3253</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3734</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.414</v>
+        <v>-2.1908</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.383</v>
+        <v>-3.9112</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9689</v>
+        <v>1.7204</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7211</v>
@@ -2170,13 +2170,13 @@
         <v>1.8556</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2444</v>
+        <v>-1.0212</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5683</v>
+        <v>-1.0965</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6761</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.0722</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.414</v>
+        <v>-5.0995</v>
       </c>
       <c r="E23" t="n">
         <v>-7.1348</v>
       </c>
       <c r="F23" t="n">
-        <v>1.7207</v>
+        <v>2.0353</v>
       </c>
       <c r="G23" t="n">
         <v>-3.3962</v>
@@ -2248,13 +2248,13 @@
         <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5386</v>
+        <v>-0.224</v>
       </c>
       <c r="T23" t="n">
         <v>-0.6326000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.094</v>
+        <v>0.4086</v>
       </c>
       <c r="V23" t="n">
         <v>1.0722</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.8398</v>
+        <v>-0.6945000000000006</v>
       </c>
       <c r="E24" t="n">
         <v>-23.7394</v>
       </c>
       <c r="F24" t="n">
-        <v>19.8994</v>
+        <v>23.0449</v>
       </c>
       <c r="G24" t="n">
         <v>1.518800000000001</v>
@@ -2314,7 +2314,7 @@
         <v>-0.07619999999999978</v>
       </c>
       <c r="O24" t="n">
-        <v>5.990499999999999</v>
+        <v>5.9905</v>
       </c>
       <c r="P24" t="n">
         <v>2.3196</v>
@@ -2326,13 +2326,13 @@
         <v>18.5562</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.2117</v>
+        <v>-3.0663</v>
       </c>
       <c r="T24" t="n">
-        <v>-6.071300000000001</v>
+        <v>-6.071199999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1406</v>
+        <v>3.004699999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.4665</v>
